--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -451,23 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad Pos 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.83356</v>
+        <v>16.81796</v>
       </c>
       <c r="D2" t="n">
-        <v>16.07146</v>
+        <v>16.58026</v>
       </c>
       <c r="E2" t="n">
-        <v>16.24262</v>
+        <v>16.76956</v>
       </c>
       <c r="F2" t="n">
-        <v>22.40599</v>
+        <v>41.77614</v>
       </c>
       <c r="G2" t="n">
-        <v>34.40533</v>
+        <v>0.05074</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.80737</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.6313</v>
+        <v>16.98121</v>
       </c>
       <c r="D3" t="n">
-        <v>15.99746</v>
+        <v>16.60238</v>
       </c>
       <c r="E3" t="n">
-        <v>16.45061</v>
+        <v>16.67215</v>
       </c>
       <c r="F3" t="n">
-        <v>21.66654</v>
+        <v>42.40715</v>
       </c>
       <c r="G3" t="n">
-        <v>34.17544</v>
+        <v>0.05152</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.85353</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.6996</v>
+        <v>16.64337</v>
       </c>
       <c r="D4" t="n">
-        <v>15.96679</v>
+        <v>16.49053</v>
       </c>
       <c r="E4" t="n">
-        <v>16.55243</v>
+        <v>16.64336</v>
       </c>
       <c r="F4" t="n">
-        <v>21.6694</v>
+        <v>42.8532</v>
       </c>
       <c r="G4" t="n">
-        <v>33.67821</v>
+        <v>0.04962</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.79683</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.73309</v>
+        <v>17.18642</v>
       </c>
       <c r="D5" t="n">
-        <v>16.5142</v>
+        <v>16.5029</v>
       </c>
       <c r="E5" t="n">
-        <v>16.31486</v>
+        <v>16.71029</v>
       </c>
       <c r="F5" t="n">
-        <v>21.22773</v>
+        <v>43.18124</v>
       </c>
       <c r="G5" t="n">
-        <v>34.27247</v>
+        <v>0.0504</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.8344</v>
       </c>
     </row>
     <row r="6">
@@ -543,19 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.45161</v>
+        <v>16.77355</v>
       </c>
       <c r="D6" t="n">
-        <v>15.9733</v>
+        <v>16.49811</v>
       </c>
       <c r="E6" t="n">
-        <v>16.57105</v>
+        <v>16.68105</v>
       </c>
       <c r="F6" t="n">
-        <v>21.70862</v>
+        <v>43.1596</v>
       </c>
       <c r="G6" t="n">
-        <v>34.17767</v>
+        <v>0.04998</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.80394</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.06838</v>
+        <v>16.73802</v>
       </c>
       <c r="D7" t="n">
-        <v>16.05008</v>
+        <v>16.4872</v>
       </c>
       <c r="E7" t="n">
-        <v>16.29833</v>
+        <v>16.57737</v>
       </c>
       <c r="F7" t="n">
-        <v>21.98234</v>
+        <v>41.18656</v>
       </c>
       <c r="G7" t="n">
-        <v>33.34566</v>
+        <v>0.05034</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.77114</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.73706</v>
+        <v>17.01805</v>
       </c>
       <c r="D8" t="n">
-        <v>16.23465</v>
+        <v>16.88394</v>
       </c>
       <c r="E8" t="n">
-        <v>16.62896</v>
+        <v>16.9624</v>
       </c>
       <c r="F8" t="n">
-        <v>21.60119</v>
+        <v>42.4058</v>
       </c>
       <c r="G8" t="n">
-        <v>34.31051</v>
+        <v>0.05132</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.80855</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.24074</v>
+        <v>16.68557</v>
       </c>
       <c r="D9" t="n">
-        <v>16.05879</v>
+        <v>16.25451</v>
       </c>
       <c r="E9" t="n">
-        <v>16.15618</v>
+        <v>16.44886</v>
       </c>
       <c r="F9" t="n">
-        <v>21.73645</v>
+        <v>42.19814</v>
       </c>
       <c r="G9" t="n">
-        <v>34.12724</v>
+        <v>0.04987</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.82593</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.78662</v>
+        <v>16.8591</v>
       </c>
       <c r="D10" t="n">
-        <v>16.10529</v>
+        <v>16.67435</v>
       </c>
       <c r="E10" t="n">
-        <v>16.45095</v>
+        <v>16.81356</v>
       </c>
       <c r="F10" t="n">
-        <v>21.34911</v>
+        <v>41.57747</v>
       </c>
       <c r="G10" t="n">
-        <v>33.66367</v>
+        <v>0.05085</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.8055</v>
       </c>
     </row>
     <row r="11">
@@ -686,26 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad Pos 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.40521</v>
+        <v>16.80824</v>
       </c>
       <c r="D12" t="n">
-        <v>16.66927</v>
+        <v>16.73396</v>
       </c>
       <c r="E12" t="n">
-        <v>16.59651</v>
+        <v>16.73874</v>
       </c>
       <c r="F12" t="n">
-        <v>42.76131</v>
+        <v>43.04967</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05072</v>
+        <v>0.04971</v>
       </c>
       <c r="H12" t="n">
-        <v>1.79431</v>
+        <v>1.83973</v>
       </c>
     </row>
     <row r="13">
@@ -715,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.95122</v>
+        <v>16.52589</v>
       </c>
       <c r="D13" t="n">
-        <v>17.03636</v>
+        <v>16.42088</v>
       </c>
       <c r="E13" t="n">
-        <v>16.4821</v>
+        <v>16.52374</v>
       </c>
       <c r="F13" t="n">
-        <v>42.44006</v>
+        <v>42.51447</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0514</v>
+        <v>0.05023</v>
       </c>
       <c r="H13" t="n">
-        <v>1.81451</v>
+        <v>1.79651</v>
       </c>
     </row>
     <row r="14">
@@ -740,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.70195</v>
+        <v>16.73317</v>
       </c>
       <c r="D14" t="n">
-        <v>16.69678</v>
+        <v>16.50317</v>
       </c>
       <c r="E14" t="n">
-        <v>16.51902</v>
+        <v>16.52265</v>
       </c>
       <c r="F14" t="n">
-        <v>42.1858</v>
+        <v>43.50924</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05107</v>
+        <v>0.05114</v>
       </c>
       <c r="H14" t="n">
-        <v>1.79001</v>
+        <v>1.80159</v>
       </c>
     </row>
     <row r="15">
@@ -765,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.97943</v>
+        <v>17.11405</v>
       </c>
       <c r="D15" t="n">
-        <v>16.33723</v>
+        <v>16.36517</v>
       </c>
       <c r="E15" t="n">
-        <v>16.69495</v>
+        <v>16.63101</v>
       </c>
       <c r="F15" t="n">
-        <v>42.19729</v>
+        <v>42.91132</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05077</v>
+        <v>0.05038</v>
       </c>
       <c r="H15" t="n">
-        <v>1.79722</v>
+        <v>1.80057</v>
       </c>
     </row>
     <row r="16">
@@ -790,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.73462</v>
+        <v>16.87359</v>
       </c>
       <c r="D16" t="n">
-        <v>16.37098</v>
+        <v>16.46599</v>
       </c>
       <c r="E16" t="n">
-        <v>16.8051</v>
+        <v>16.57267</v>
       </c>
       <c r="F16" t="n">
-        <v>42.39747</v>
+        <v>43.52777</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05027</v>
+        <v>0.0506</v>
       </c>
       <c r="H16" t="n">
-        <v>1.83563</v>
+        <v>1.84929</v>
       </c>
     </row>
     <row r="17">
@@ -815,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.00159</v>
+        <v>16.84715</v>
       </c>
       <c r="D17" t="n">
-        <v>16.58118</v>
+        <v>16.74586</v>
       </c>
       <c r="E17" t="n">
-        <v>17.02806</v>
+        <v>16.7688</v>
       </c>
       <c r="F17" t="n">
-        <v>41.73139</v>
+        <v>42.52047</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04971</v>
+        <v>0.05087</v>
       </c>
       <c r="H17" t="n">
-        <v>1.83813</v>
+        <v>1.81608</v>
       </c>
     </row>
     <row r="18">
@@ -840,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.77943</v>
+        <v>16.68032</v>
       </c>
       <c r="D18" t="n">
-        <v>16.44542</v>
+        <v>16.48375</v>
       </c>
       <c r="E18" t="n">
-        <v>16.89083</v>
+        <v>16.66616</v>
       </c>
       <c r="F18" t="n">
-        <v>42.48404</v>
+        <v>43.34166</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05047</v>
+        <v>0.04994</v>
       </c>
       <c r="H18" t="n">
-        <v>1.82247</v>
+        <v>1.87223</v>
       </c>
     </row>
     <row r="19">
@@ -865,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.11178</v>
+        <v>17.1417</v>
       </c>
       <c r="D19" t="n">
-        <v>16.39343</v>
+        <v>16.20022</v>
       </c>
       <c r="E19" t="n">
-        <v>16.87075</v>
+        <v>16.81117</v>
       </c>
       <c r="F19" t="n">
-        <v>42.23065</v>
+        <v>41.93215</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05083</v>
+        <v>0.05014</v>
       </c>
       <c r="H19" t="n">
-        <v>1.83018</v>
+        <v>1.79859</v>
       </c>
     </row>
     <row r="20">
@@ -890,22 +922,782 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.85522</v>
+        <v>16.8198</v>
       </c>
       <c r="D20" t="n">
-        <v>16.43844</v>
+        <v>16.23847</v>
       </c>
       <c r="E20" t="n">
-        <v>16.7771</v>
+        <v>16.579</v>
       </c>
       <c r="F20" t="n">
-        <v>42.11755</v>
+        <v>42.25203</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05031</v>
+        <v>0.05023</v>
       </c>
       <c r="H20" t="n">
-        <v>1.79945</v>
+        <v>1.84894</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad Pos 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>16.38525</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.54768</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.77362</v>
+      </c>
+      <c r="F22" t="n">
+        <v>254.92392</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15.75261</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.50879</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.64068</v>
+      </c>
+      <c r="F23" t="n">
+        <v>253.20296</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15.7671</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15.49373</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.61638</v>
+      </c>
+      <c r="F24" t="n">
+        <v>250.30765</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15.98711</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15.7015</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.83497</v>
+      </c>
+      <c r="F25" t="n">
+        <v>256.10456</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15.69219</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.56294</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.64748</v>
+      </c>
+      <c r="F26" t="n">
+        <v>252.85835</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>15.73717</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15.45112</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.54205</v>
+      </c>
+      <c r="F27" t="n">
+        <v>257.41175</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15.5422</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15.33889</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.39211</v>
+      </c>
+      <c r="F28" t="n">
+        <v>252.57078</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>16.1797</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.5092</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.51261</v>
+      </c>
+      <c r="F29" t="n">
+        <v>252.27315</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>15.69828</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.56099</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.57994</v>
+      </c>
+      <c r="F30" t="n">
+        <v>256.93182</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace Pos 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.66519</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.0653</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.13122</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.01791</v>
+      </c>
+      <c r="G32" t="n">
+        <v>33.5549</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.10852</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.09733</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.31805</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.80678</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.86169</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17.05272</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.30356</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.32404</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.61858</v>
+      </c>
+      <c r="G34" t="n">
+        <v>33.65411</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.6436</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.02826</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.45756</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.66863</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.62214</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.66013</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.12002</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.44055</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.76629</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.38698</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.69024</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.1317</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.25811</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.64687</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.46467</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.70484</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15.67498</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.17572</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.98469</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.45593</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.9111</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.00876</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.48973</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.39375</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.55868</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.56585</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.07497</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.44609</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.60239</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.58421</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Via Pos 1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.60708</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.13207</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.60697</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.09399</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.6181</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.08796</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.59955</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.1293</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.59904</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.11361</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.60685</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.12818</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.60614</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.10751</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.60332</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.10853</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.6043500000000001</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.13799</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Landing Pad 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>16.87101</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16.74224</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.84109</v>
+      </c>
+      <c r="F52" t="n">
+        <v>41.81928</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>16.8957</v>
+      </c>
+      <c r="D53" t="n">
+        <v>16.41853</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.46442</v>
+      </c>
+      <c r="F53" t="n">
+        <v>42.81593</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>16.92897</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.85591</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.89819</v>
+      </c>
+      <c r="F54" t="n">
+        <v>42.01038</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>16.72636</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.54865</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.70066</v>
+      </c>
+      <c r="F55" t="n">
+        <v>42.71966</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>16.80963</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.40856</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.72334</v>
+      </c>
+      <c r="F56" t="n">
+        <v>43.48177</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>16.59695</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.38603</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.56223</v>
+      </c>
+      <c r="F57" t="n">
+        <v>42.50018</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.8668</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.60726</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.6161</v>
+      </c>
+      <c r="F58" t="n">
+        <v>43.19296</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>17.20331</v>
+      </c>
+      <c r="D59" t="n">
+        <v>16.44723</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.76537</v>
+      </c>
+      <c r="F59" t="n">
+        <v>42.41588</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16.8036</v>
+      </c>
+      <c r="D60" t="n">
+        <v>16.6542</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.76899</v>
+      </c>
+      <c r="F60" t="n">
+        <v>42.96432</v>
       </c>
     </row>
   </sheetData>
